--- a/التقارير-الاسبوعية/KAZ Project Weekly EHS Report.xlsx
+++ b/التقارير-الاسبوعية/KAZ Project Weekly EHS Report.xlsx
@@ -7993,9 +7993,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00459C07-14A7-4144-BD20-D68B4EF15230}">
+<worksheet xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00459C07-14A7-4144-BD20-D68B4EF15230}">
   <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultRowHeight="12.5" ns3:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.81640625" customWidth="1"/>
     <col min="2" max="3" width="8.81640625" customWidth="1"/>
@@ -8005,7 +8005,7 @@
     <col min="11" max="11" width="42.0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14" ns3:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="14" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -8021,7 +8021,7 @@
         <f>"Week "&amp;TEXT('EHS KPI'!$G$7,"00")&amp;"  |  "&amp;TEXT('EHS KPI'!$G$8,"dd mmm yyyy")&amp;"  -  "&amp;TEXT('EHS KPI'!$G$9,"dd mmm yyyy")</f>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="14" ns3:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="14" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -8066,7 +8066,7 @@
         </is>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.5" ns3:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -8081,7 +8081,7 @@
         <f>SUM(B3:H3)</f>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="15.5" ns3:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>3</v>
       </c>
@@ -8096,7 +8096,7 @@
         <f>SUM(B4:H4)</f>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="15.5" ns3:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
         <v>4</v>
       </c>
@@ -8111,7 +8111,7 @@
         <f>SUM(B5:H5)</f>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="15.5" ns3:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>5</v>
       </c>
@@ -8126,7 +8126,7 @@
         <f>SUM(B6:H6)</f>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="15.5" ns3:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="30" t="s">
         <v>6</v>
       </c>
@@ -8141,7 +8141,7 @@
         <f>SUM(B7:H7)</f>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.5" ns3:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
         <v>7</v>
       </c>
@@ -8156,7 +8156,7 @@
         <f>SUM(B8:H8)</f>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.5" ns3:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="30" t="s">
         <v>8</v>
       </c>
@@ -8171,7 +8171,7 @@
         <f>SUM(B9:H9)</f>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.5" ns3:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="30" t="s">
         <v>113</v>
       </c>
@@ -8186,7 +8186,7 @@
         <f>SUM(B10:H10)</f>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.5" ns3:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="19"/>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -8213,9 +8213,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AG53"/>
-  <sheetFormatPr defaultRowHeight="12.5" ns3:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="4.1796875" customWidth="1"/>
@@ -8227,7 +8227,7 @@
     <col min="23" max="23" width="12.0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="18.75" customHeight="1" ns3:dyDescent="0.25">
+    <row r="1" spans="1:27" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="28" t="s">
         <v>9</v>
       </c>
@@ -8262,7 +8262,7 @@
       <c r="Z1" s="28"/>
       <c r="AA1" s="28"/>
     </row>
-    <row r="2" spans="1:33" ht="15.5" ns3:dyDescent="0.35">
+    <row r="2" spans="1:33" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -8356,7 +8356,7 @@
       <c r="AF2" s="24"/>
       <c r="AG2" s="24"/>
     </row>
-    <row r="3" spans="1:23" ht="15.5" ns3:dyDescent="0.35">
+    <row r="3" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
         <v>12</v>
       </c>
@@ -8413,7 +8413,7 @@
         <f>SUM(P3:V3)</f>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15.5" ns3:dyDescent="0.35">
+    <row r="4" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>12</v>
       </c>
@@ -8470,7 +8470,7 @@
         <f>SUM(P4:V4)</f>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="15.5" ns3:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
         <v>14</v>
       </c>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="N5" s="21"/>
     </row>
-    <row r="6" spans="1:14" ht="15.5" ns3:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>15</v>
       </c>
@@ -8530,7 +8530,7 @@
       </c>
       <c r="N6" s="21"/>
     </row>
-    <row r="7" spans="1:14" ht="15.5" ns3:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="19" t="s">
         <v>16</v>
       </c>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="N7" s="21"/>
     </row>
-    <row r="8" spans="1:14" ht="15.5" ns3:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
         <v>17</v>
       </c>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="N8" s="21"/>
     </row>
-    <row r="9" spans="1:14" ht="15.5" ns3:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="19" t="s">
         <v>18</v>
       </c>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="N9" s="21"/>
     </row>
-    <row r="10" spans="1:14" ht="15.5" ns3:dyDescent="0.35">
+    <row r="10" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
         <v>19</v>
       </c>
@@ -8650,61 +8650,61 @@
       </c>
       <c r="N10" s="21"/>
     </row>
-    <row r="11" spans="14:14" ns3:dyDescent="0.25">
+    <row r="11" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N11" s="21"/>
     </row>
-    <row r="12" spans="14:14" ns3:dyDescent="0.25">
+    <row r="12" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N12" s="21"/>
     </row>
-    <row r="13" spans="14:14" ns3:dyDescent="0.25">
+    <row r="13" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N13" s="21"/>
     </row>
-    <row r="14" spans="14:14" ns3:dyDescent="0.25">
+    <row r="14" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N14" s="21"/>
     </row>
-    <row r="15" spans="14:14" ns3:dyDescent="0.25">
+    <row r="15" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N15" s="21"/>
     </row>
-    <row r="16" spans="14:14" ns3:dyDescent="0.25">
+    <row r="16" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N16" s="21"/>
     </row>
-    <row r="17" spans="14:14" ns3:dyDescent="0.25">
+    <row r="17" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N17" s="21"/>
     </row>
-    <row r="18" spans="14:14" ns3:dyDescent="0.25">
+    <row r="18" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N18" s="21"/>
     </row>
-    <row r="19" spans="14:14" ns3:dyDescent="0.25">
+    <row r="19" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N19" s="21"/>
     </row>
-    <row r="20" spans="14:14" ns3:dyDescent="0.25">
+    <row r="20" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N20" s="21"/>
     </row>
-    <row r="21" spans="14:14" ns3:dyDescent="0.25">
+    <row r="21" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N21" s="21"/>
     </row>
-    <row r="22" spans="14:14" ns3:dyDescent="0.25">
+    <row r="22" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N22" s="21"/>
     </row>
-    <row r="23" spans="14:14" ns3:dyDescent="0.25">
+    <row r="23" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N23" s="21"/>
     </row>
-    <row r="24" spans="14:14" ns3:dyDescent="0.25">
+    <row r="24" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N24" s="21"/>
     </row>
-    <row r="25" spans="14:14" ns3:dyDescent="0.25">
+    <row r="25" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N25" s="21"/>
     </row>
-    <row r="26" spans="14:14" ns3:dyDescent="0.25">
+    <row r="26" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N26" s="21"/>
     </row>
-    <row r="27" spans="14:14" ns3:dyDescent="0.25">
+    <row r="27" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N27" s="21"/>
     </row>
-    <row r="28" spans="14:14" ns3:dyDescent="0.25">
+    <row r="28" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N28" s="21"/>
     </row>
-    <row r="29" spans="1:27" ns3:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="21"/>
       <c r="B29" s="21"/>
       <c r="C29" s="21"/>
@@ -8733,7 +8733,7 @@
       <c r="Z29" s="21"/>
       <c r="AA29" s="21"/>
     </row>
-    <row r="30" spans="1:27" ns3:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="21"/>
       <c r="B30" s="21"/>
       <c r="C30" s="21"/>
@@ -8762,7 +8762,7 @@
       <c r="Z30" s="21"/>
       <c r="AA30" s="21"/>
     </row>
-    <row r="31" spans="1:27" ht="14.5" thickBot="1" ns3:dyDescent="0.3">
+    <row r="31" spans="1:27" ht="14.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="29" t="s">
         <v>20</v>
       </c>
@@ -8795,7 +8795,7 @@
       <c r="Z31" s="29"/>
       <c r="AA31" s="29"/>
     </row>
-    <row r="32" spans="1:23" ht="15.5" ns3:dyDescent="0.35">
+    <row r="32" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="19" t="s">
         <v>1</v>
       </c>
@@ -8884,7 +8884,7 @@
         </is>
       </c>
     </row>
-    <row r="33" spans="1:23" ht="15.5" ns3:dyDescent="0.35">
+    <row r="33" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="19" t="s">
         <v>22</v>
       </c>
@@ -8927,7 +8927,7 @@
         <f>SUM(P33:V33)</f>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="15.5" ns3:dyDescent="0.35">
+    <row r="34" spans="1:23" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="19" t="s">
         <v>24</v>
       </c>
@@ -8970,7 +8970,7 @@
         <f>SUM(P34:V34)</f>
       </c>
     </row>
-    <row r="35" spans="14:23" ht="15.5" ns3:dyDescent="0.35">
+    <row r="35" spans="14:23" ht="15.5" x14ac:dyDescent="0.35">
       <c r="N35" s="21"/>
       <c r="O35" s="19" t="s">
         <v>26</v>
@@ -8986,58 +8986,58 @@
         <f>SUM(P35:V35)</f>
       </c>
     </row>
-    <row r="36" spans="14:14" ns3:dyDescent="0.25">
+    <row r="36" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N36" s="21"/>
     </row>
-    <row r="37" spans="14:14" ns3:dyDescent="0.25">
+    <row r="37" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N37" s="21"/>
     </row>
-    <row r="38" spans="14:14" ns3:dyDescent="0.25">
+    <row r="38" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N38" s="21"/>
     </row>
-    <row r="39" spans="14:14" ns3:dyDescent="0.25">
+    <row r="39" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N39" s="21"/>
     </row>
-    <row r="40" spans="14:14" ns3:dyDescent="0.25">
+    <row r="40" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N40" s="21"/>
     </row>
-    <row r="41" spans="14:14" ns3:dyDescent="0.25">
+    <row r="41" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N41" s="21"/>
     </row>
-    <row r="42" spans="14:14" ns3:dyDescent="0.25">
+    <row r="42" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N42" s="21"/>
     </row>
-    <row r="43" spans="14:14" ns3:dyDescent="0.25">
+    <row r="43" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N43" s="21"/>
     </row>
-    <row r="44" spans="14:14" ns3:dyDescent="0.25">
+    <row r="44" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N44" s="21"/>
     </row>
-    <row r="45" spans="14:14" ns3:dyDescent="0.25">
+    <row r="45" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N45" s="21"/>
     </row>
-    <row r="46" spans="14:14" ns3:dyDescent="0.25">
+    <row r="46" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N46" s="21"/>
     </row>
-    <row r="47" spans="14:14" ns3:dyDescent="0.25">
+    <row r="47" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N47" s="21"/>
     </row>
-    <row r="48" spans="14:14" ns3:dyDescent="0.25">
+    <row r="48" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N48" s="21"/>
     </row>
-    <row r="49" spans="14:14" ns3:dyDescent="0.25">
+    <row r="49" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N49" s="21"/>
     </row>
-    <row r="50" spans="14:14" ns3:dyDescent="0.25">
+    <row r="50" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N50" s="21"/>
     </row>
-    <row r="51" spans="14:14" ns3:dyDescent="0.25">
+    <row r="51" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N51" s="21"/>
     </row>
-    <row r="52" spans="14:14" ns3:dyDescent="0.25">
+    <row r="52" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N52" s="21"/>
     </row>
-    <row r="53" spans="14:14" ns3:dyDescent="0.25">
+    <row r="53" spans="14:14" x14ac:dyDescent="0.25">
       <c r="N53" s="21"/>
     </row>
   </sheetData>
@@ -9055,9 +9055,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{E2791000-E506-42F5-9E0C-3C20AFC66042}">
+<worksheet xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2791000-E506-42F5-9E0C-3C20AFC66042}">
   <dimension ref="A1:I41"/>
-  <sheetFormatPr defaultRowHeight="12.5" ns3:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.453125" customWidth="1"/>
     <col min="2" max="2" width="13.1796875" customWidth="1"/>
@@ -9070,7 +9070,7 @@
     <col min="9" max="9" width="11.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="37.5" customHeight="1" ns3:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
         <v>27</v>
       </c>
@@ -9099,7 +9099,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="83.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="83.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="51" t="s">
         <v>95</v>
       </c>
@@ -9126,7 +9126,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="79.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="51" t="s">
         <v>96</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="109" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="109" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="51" t="s">
         <v>97</v>
       </c>
@@ -9182,7 +9182,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="79.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="51" t="s">
         <v>98</v>
       </c>
@@ -9195,7 +9195,7 @@
       <c r="H5" s="37"/>
       <c r="I5" s="55"/>
     </row>
-    <row r="6" spans="1:9" ht="111.65" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="111.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="51" t="s">
         <v>99</v>
       </c>
@@ -9208,7 +9208,7 @@
       <c r="H6" s="37"/>
       <c r="I6" s="55"/>
     </row>
-    <row r="7" spans="1:9" ht="99" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="99" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="51" t="s">
         <v>102</v>
       </c>
@@ -9221,7 +9221,7 @@
       <c r="H7" s="37"/>
       <c r="I7" s="55"/>
     </row>
-    <row r="8" spans="1:9" ht="132" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="132" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="51" t="s">
         <v>103</v>
       </c>
@@ -9234,7 +9234,7 @@
       <c r="H8" s="37"/>
       <c r="I8" s="55"/>
     </row>
-    <row r="9" spans="1:9" ht="138" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="138" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="51" t="s">
         <v>104</v>
       </c>
@@ -9247,7 +9247,7 @@
       <c r="H9" s="37"/>
       <c r="I9" s="55"/>
     </row>
-    <row r="10" spans="1:9" ht="96.65" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="10" spans="1:9" ht="96.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="51" t="s">
         <v>105</v>
       </c>
@@ -9260,7 +9260,7 @@
       <c r="H10" s="37"/>
       <c r="I10" s="55"/>
     </row>
-    <row r="11" spans="1:9" ht="143.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="143.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="51" t="s">
         <v>106</v>
       </c>
@@ -9273,7 +9273,7 @@
       <c r="H11" s="37"/>
       <c r="I11" s="38"/>
     </row>
-    <row r="12" spans="1:9" ht="143.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="143.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="51" t="s">
         <v>107</v>
       </c>
@@ -9286,7 +9286,7 @@
       <c r="H12" s="37"/>
       <c r="I12" s="38"/>
     </row>
-    <row r="13" spans="1:9" ht="12.75" hidden="1" customHeight="1" ns3:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="12.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="51" t="s">
         <v>108</v>
       </c>
@@ -9299,7 +9299,7 @@
       <c r="H13" s="37"/>
       <c r="I13" s="38"/>
     </row>
-    <row r="14" spans="1:9" ht="102" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="51" t="s">
         <v>109</v>
       </c>
@@ -9312,7 +9312,7 @@
       <c r="H14" s="37"/>
       <c r="I14" s="38"/>
     </row>
-    <row r="15" spans="1:9" ht="143.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="143.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="51" t="s">
         <v>110</v>
       </c>
@@ -9325,7 +9325,7 @@
       <c r="H15" s="37"/>
       <c r="I15" s="38"/>
     </row>
-    <row r="16" spans="1:9" ht="143.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="143.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="51" t="s">
         <v>111</v>
       </c>
@@ -9338,7 +9338,7 @@
       <c r="H16" s="37"/>
       <c r="I16" s="38"/>
     </row>
-    <row r="17" spans="1:9" ht="95.4" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="95.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="51" t="s">
         <v>112</v>
       </c>
@@ -9351,7 +9351,7 @@
       <c r="H17" s="37"/>
       <c r="I17" s="38"/>
     </row>
-    <row r="18" spans="1:9" ht="89.4" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="89.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="51"/>
       <c r="B18" s="52"/>
       <c r="C18" s="44"/>
@@ -9362,7 +9362,7 @@
       <c r="H18" s="37"/>
       <c r="I18" s="38"/>
     </row>
-    <row r="19" spans="1:9" ht="61.25" customHeight="1" ns3:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="61.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="85"/>
       <c r="B19" s="86"/>
       <c r="C19" s="86"/>
@@ -9373,7 +9373,7 @@
       <c r="H19" s="86"/>
       <c r="I19" s="87"/>
     </row>
-    <row r="20" spans="1:9" ht="143.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="143.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="39"/>
       <c r="B20" s="59"/>
       <c r="C20" s="44"/>
@@ -9384,7 +9384,7 @@
       <c r="H20" s="37"/>
       <c r="I20" s="60"/>
     </row>
-    <row r="21" spans="1:9" ht="121.75" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="121.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="39"/>
       <c r="B21" s="59"/>
       <c r="C21" s="61"/>
@@ -9395,7 +9395,7 @@
       <c r="H21" s="37"/>
       <c r="I21" s="60"/>
     </row>
-    <row r="22" spans="1:9" ht="100.75" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="100.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="39"/>
       <c r="B22" s="59"/>
       <c r="C22" s="44"/>
@@ -9406,7 +9406,7 @@
       <c r="H22" s="37"/>
       <c r="I22" s="60"/>
     </row>
-    <row r="23" spans="1:9" s="45" customFormat="1" ht="143.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="23" spans="1:9" s="45" customFormat="1" ht="143.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="39"/>
       <c r="B23" s="59"/>
       <c r="C23" s="44"/>
@@ -9417,7 +9417,7 @@
       <c r="H23" s="37"/>
       <c r="I23" s="60"/>
     </row>
-    <row r="24" spans="1:9" s="46" customFormat="1" ht="143.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="24" spans="1:9" s="46" customFormat="1" ht="143.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="39"/>
       <c r="B24" s="59"/>
       <c r="C24" s="43"/>
@@ -9428,7 +9428,7 @@
       <c r="H24"/>
       <c r="I24" s="60"/>
     </row>
-    <row r="25" spans="1:9" s="46" customFormat="1" ht="143.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="25" spans="1:9" s="46" customFormat="1" ht="143.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="39"/>
       <c r="B25" s="59"/>
       <c r="C25" s="44"/>
@@ -9439,7 +9439,7 @@
       <c r="H25" s="37"/>
       <c r="I25" s="60"/>
     </row>
-    <row r="26" spans="1:9" s="46" customFormat="1" ht="143.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="26" spans="1:9" s="46" customFormat="1" ht="143.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="39"/>
       <c r="B26" s="59"/>
       <c r="C26" s="44"/>
@@ -9450,7 +9450,7 @@
       <c r="H26" s="37"/>
       <c r="I26" s="60"/>
     </row>
-    <row r="27" spans="1:9" s="46" customFormat="1" ht="143.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="27" spans="1:9" s="46" customFormat="1" ht="143.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="39"/>
       <c r="B27" s="59"/>
       <c r="C27" s="44"/>
@@ -9461,7 +9461,7 @@
       <c r="H27" s="37"/>
       <c r="I27" s="60"/>
     </row>
-    <row r="28" spans="1:9" ht="102.65" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="102.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="39"/>
       <c r="B28" s="59"/>
       <c r="C28" s="44"/>
@@ -9472,7 +9472,7 @@
       <c r="H28" s="37"/>
       <c r="I28" s="60"/>
     </row>
-    <row r="29" spans="1:9" ht="91.75" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="91.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="39"/>
       <c r="B29" s="59"/>
       <c r="C29" s="44"/>
@@ -9483,7 +9483,7 @@
       <c r="H29" s="37"/>
       <c r="I29" s="60"/>
     </row>
-    <row r="30" spans="1:9" ht="118.75" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="118.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="39"/>
       <c r="B30" s="59"/>
       <c r="C30" s="44"/>
@@ -9494,7 +9494,7 @@
       <c r="H30" s="37"/>
       <c r="I30" s="60"/>
     </row>
-    <row r="31" spans="1:9" ht="96" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="96" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="39"/>
       <c r="B31" s="59"/>
       <c r="C31" s="34"/>
@@ -9505,7 +9505,7 @@
       <c r="H31" s="37"/>
       <c r="I31" s="38"/>
     </row>
-    <row r="32" spans="1:9" ht="102" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="32" spans="1:9" ht="102" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="63"/>
       <c r="B32" s="59"/>
       <c r="C32" s="44"/>
@@ -9516,7 +9516,7 @@
       <c r="H32" s="37"/>
       <c r="I32" s="38"/>
     </row>
-    <row r="33" spans="1:9" ht="110.4" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="33" spans="1:9" ht="110.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="63"/>
       <c r="B33" s="59"/>
       <c r="C33" s="44"/>
@@ -9527,7 +9527,7 @@
       <c r="H33" s="37"/>
       <c r="I33" s="38"/>
     </row>
-    <row r="34" spans="1:9" ht="93" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="93" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="63"/>
       <c r="B34" s="59"/>
       <c r="C34" s="44"/>
@@ -9538,7 +9538,7 @@
       <c r="H34" s="37"/>
       <c r="I34" s="38"/>
     </row>
-    <row r="35" spans="1:9" ht="93" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="35" spans="1:9" ht="93" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="63"/>
       <c r="B35" s="59"/>
       <c r="C35" s="44"/>
@@ -9549,7 +9549,7 @@
       <c r="H35" s="37"/>
       <c r="I35" s="38"/>
     </row>
-    <row r="36" spans="1:9" ht="93" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="93" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="63"/>
       <c r="B36" s="59"/>
       <c r="C36" s="44"/>
@@ -9560,7 +9560,7 @@
       <c r="H36" s="37"/>
       <c r="I36" s="38"/>
     </row>
-    <row r="37" spans="1:9" ht="93" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="37" spans="1:9" ht="93" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="63"/>
       <c r="B37" s="59"/>
       <c r="C37" s="44"/>
@@ -9571,7 +9571,7 @@
       <c r="H37" s="37"/>
       <c r="I37" s="38"/>
     </row>
-    <row r="38" spans="1:9" ht="93" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="38" spans="1:9" ht="93" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="63"/>
       <c r="B38" s="59"/>
       <c r="C38" s="44"/>
@@ -9582,7 +9582,7 @@
       <c r="H38" s="37"/>
       <c r="I38" s="38"/>
     </row>
-    <row r="39" spans="1:9" ht="93" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="39" spans="1:9" ht="93" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="63"/>
       <c r="B39" s="59"/>
       <c r="C39" s="44"/>
@@ -9593,7 +9593,7 @@
       <c r="H39" s="37"/>
       <c r="I39" s="38"/>
     </row>
-    <row r="40" spans="1:9" ht="93" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="40" spans="1:9" ht="93" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="63"/>
       <c r="B40" s="59"/>
       <c r="C40" s="44"/>
@@ -9604,7 +9604,7 @@
       <c r="H40" s="37"/>
       <c r="I40" s="38"/>
     </row>
-    <row r="41" spans="1:9" ht="93" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="41" spans="1:9" ht="93" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="63"/>
       <c r="B41" s="59"/>
       <c r="C41" s="44"/>
@@ -9653,7 +9653,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Geçersiz Değer" error="Lütfen listeden seçin: open veya closed" sqref="I2:I97" ns2:uid="{766463DC-64DA-4446-A05E-4404C3E1C46C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Geçersiz Değer" error="Lütfen listeden seçin: open veya closed" sqref="I2:I97" xr:uid="{766463DC-64DA-4446-A05E-4404C3E1C46C}">
       <formula1>"open,closed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9663,9 +9663,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:S32"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" ns3:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="12" customWidth="1"/>
     <col min="3" max="4" width="7" bestFit="1" customWidth="1"/>
@@ -9679,8 +9679,8 @@
     <col min="10" max="11" width="11.0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" ns3:dyDescent="0.25"/>
-    <row r="2" spans="7:11" ht="17.25" customHeight="1" ns3:dyDescent="0.35">
+    <row r="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="7:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="G2" s="9" t="s">
         <v>35</v>
       </c>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="K2" s="2"/>
     </row>
-    <row r="3" spans="1:11" ht="17.25" customHeight="1" ns3:dyDescent="0.4">
+    <row r="3" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="1"/>
       <c r="B3" s="82" t="s">
         <v>37</v>
@@ -9704,7 +9704,7 @@
       </c>
       <c r="K3" s="2"/>
     </row>
-    <row r="4" spans="1:11" ht="17.25" customHeight="1" ns3:dyDescent="0.4">
+    <row r="4" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="1"/>
       <c r="B4" s="82" t="s">
         <v>38</v>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="2:11" ht="17.25" customHeight="1" ns3:dyDescent="0.35">
+    <row r="5" spans="2:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="82" t="s">
         <v>39</v>
       </c>
@@ -9733,7 +9733,7 @@
       <c r="H5" s="83"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="2:8" ht="14" ns3:dyDescent="0.25">
+    <row r="6" spans="2:8" ht="14" x14ac:dyDescent="0.25">
       <c r="B6" s="82" t="s">
         <v>40</v>
       </c>
@@ -9756,7 +9756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15" ht="18" customHeight="1" ns3:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="1" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
       <c r="N8" s="16"/>
       <c r="O8" s="16"/>
     </row>
-    <row r="9" spans="1:19" ht="9" customHeight="1" ns3:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12"/>
       <c r="B9" s="1" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
       <c r="R9" s="12"/>
       <c r="S9" s="12"/>
     </row>
-    <row r="10" spans="1:11" ht="18" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="69" t="s">
         <v>41</v>
       </c>
@@ -9821,7 +9821,7 @@
       <c r="J10" s="69"/>
       <c r="K10" s="69"/>
     </row>
-    <row r="11" spans="1:10" ht="13" thickBot="1" ns3:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3" t="inlineStr">
@@ -9865,7 +9865,7 @@
         </is>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="17.25" customHeight="1" ns3:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>55</v>
       </c>
@@ -9895,7 +9895,7 @@
         <f>SUM(C12:I12)</f>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="42" customHeight="1" ns3:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="77" t="s">
         <v>56</v>
       </c>
@@ -9925,7 +9925,7 @@
         <f>SUM(C13:I13)</f>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.75" customHeight="1" ns3:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="79" t="s">
         <v>58</v>
       </c>
@@ -9955,7 +9955,7 @@
         <f>SUM(J12,J13)</f>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="24.75" customHeight="1" ns3:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="75"/>
       <c r="B15" s="75"/>
       <c r="C15" s="6"/>
@@ -9968,7 +9968,7 @@
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
     </row>
-    <row r="16" spans="1:11" ht="8.25" customHeight="1" ns3:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
       <c r="C16" s="6"/>
@@ -9981,7 +9981,7 @@
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
     </row>
-    <row r="17" spans="1:11" ht="18" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="69" t="s">
         <v>59</v>
       </c>
@@ -9996,7 +9996,7 @@
       <c r="J17" s="69"/>
       <c r="K17" s="69"/>
     </row>
-    <row r="18" spans="1:10" ht="13.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="inlineStr">
@@ -10040,7 +10040,7 @@
         </is>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="13.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="64" t="s">
         <v>11</v>
       </c>
@@ -10070,7 +10070,7 @@
         <f>SUM(C19:I19)</f>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="13.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="20" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="64" t="s">
         <v>12</v>
       </c>
@@ -10100,7 +10100,7 @@
         <f>SUM(C20:I20)</f>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="13.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="21" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="64" t="s">
         <v>14</v>
       </c>
@@ -10130,7 +10130,7 @@
         <f>SUM(C21:I21)</f>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="13.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="22" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="64" t="s">
         <v>15</v>
       </c>
@@ -10160,7 +10160,7 @@
         <f>SUM(C22:I22)</f>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="13.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="64" t="s">
         <v>16</v>
       </c>
@@ -10190,7 +10190,7 @@
         <f>SUM(C23:I23)</f>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="13.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="24" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="64" t="s">
         <v>17</v>
       </c>
@@ -10220,7 +10220,7 @@
         <f>SUM(C24:I24)</f>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="13.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="25" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="64" t="s">
         <v>18</v>
       </c>
@@ -10250,7 +10250,7 @@
         <f>SUM(C25:I25)</f>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="13.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="26" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="64" t="s">
         <v>19</v>
       </c>
@@ -10280,7 +10280,7 @@
         <f>SUM(C26:I26)</f>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="9.75" customHeight="1" ns3:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="68"/>
       <c r="B27" s="68"/>
       <c r="C27" s="68"/>
@@ -10293,7 +10293,7 @@
       <c r="J27" s="68"/>
       <c r="K27" s="68"/>
     </row>
-    <row r="28" spans="1:11" ht="18" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="69" t="s">
         <v>0</v>
       </c>
@@ -10308,7 +10308,7 @@
       <c r="J28" s="69"/>
       <c r="K28" s="69"/>
     </row>
-    <row r="29" spans="1:10" ht="13.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="inlineStr">
@@ -10352,7 +10352,7 @@
         </is>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="13.5" customHeight="1" ns3:dyDescent="0.25">
+    <row r="30" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="71" t="s">
         <v>69</v>
       </c>
@@ -10382,7 +10382,7 @@
         <f>IF(J14&lt;&gt;0,(J19+J20)*200000/J14,0)</f>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="13.5" customHeight="1" ns3:dyDescent="0.25">
+    <row r="31" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="73" t="s">
         <v>70</v>
       </c>
@@ -10412,7 +10412,7 @@
         <f>IF(J14&lt;&gt;0,(SUM(J20:J22))*200000/J14,0)</f>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="13.5" customHeight="1" thickBot="1" ns3:dyDescent="0.3">
+    <row r="32" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="66" t="s">
         <v>71</v>
       </c>
@@ -10442,10 +10442,10 @@
         <f>IF(J14&lt;&gt;0,J26*1000/J14,0)</f>
       </c>
     </row>
-    <row r="35" ht="18" customHeight="1" ns3:dyDescent="0.25"/>
-    <row r="36" ht="17.25" customHeight="1" ns3:dyDescent="0.25"/>
-    <row r="37" ht="17.25" customHeight="1" ns3:dyDescent="0.25"/>
-    <row r="38" ht="17.25" customHeight="1" ns3:dyDescent="0.25"/>
+    <row r="35" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="45">
     <mergeCell ref="B3:F3"/>
@@ -10509,9 +10509,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L10"/>
-  <sheetFormatPr defaultRowHeight="12.5" ns3:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="8.81640625" customWidth="1"/>
@@ -10521,7 +10521,7 @@
     <col min="12" max="12" width="42.0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14" ns3:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="14" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
@@ -10538,7 +10538,7 @@
         <f>"Week "&amp;TEXT('EHS KPI'!$G$7,"00")&amp;"  |  "&amp;TEXT('EHS KPI'!$G$8,"dd mmm yyyy")&amp;"  -  "&amp;TEXT('EHS KPI'!$G$9,"dd mmm yyyy")</f>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="14" ns3:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="14" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
         <v>1</v>
       </c>
@@ -10583,7 +10583,7 @@
         </is>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.5" ns3:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="19" t="s">
         <v>72</v>
       </c>
@@ -10603,7 +10603,7 @@
         </is>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.5" ns3:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>74</v>
       </c>
@@ -10623,7 +10623,7 @@
         </is>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.5" ns3:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="19" t="s">
         <v>76</v>
       </c>
@@ -10643,7 +10643,7 @@
         </is>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.5" ns3:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>78</v>
       </c>
@@ -10663,7 +10663,7 @@
         </is>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.5" ns3:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="31" t="s">
         <v>79</v>
       </c>
@@ -10683,7 +10683,7 @@
         </is>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.5" ns3:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="31" t="s">
         <v>80</v>
       </c>
@@ -10703,7 +10703,7 @@
         </is>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.5" ns3:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="31" t="s">
         <v>81</v>
       </c>
@@ -10723,7 +10723,7 @@
         </is>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.5" ns3:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
         <v>82</v>
       </c>
